--- a/costs.xlsx
+++ b/costs.xlsx
@@ -481,35 +481,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>37.3</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="F2" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="H2" t="n">
-        <v>619</v>
+        <v>158</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>1395</v>
       </c>
       <c r="J2" t="n">
-        <v>838</v>
+        <v>503</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -485,31 +485,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="E2" t="n">
-        <v>186</v>
+        <v>330</v>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>266</v>
       </c>
       <c r="G2" t="n">
-        <v>289</v>
+        <v>540</v>
       </c>
       <c r="H2" t="n">
-        <v>158</v>
+        <v>354</v>
       </c>
       <c r="I2" t="n">
-        <v>1395</v>
+        <v>2896</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>898</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="E2" t="n">
         <v>330</v>
@@ -506,10 +506,10 @@
         <v>354</v>
       </c>
       <c r="I2" t="n">
-        <v>2896</v>
+        <v>4458</v>
       </c>
       <c r="J2" t="n">
-        <v>898</v>
+        <v>1232</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -485,31 +485,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="C2" t="n">
-        <v>68.5</v>
+        <v>102.5</v>
       </c>
       <c r="D2" t="n">
-        <v>6.85</v>
+        <v>10.25</v>
       </c>
       <c r="E2" t="n">
-        <v>330</v>
+        <v>461</v>
       </c>
       <c r="F2" t="n">
-        <v>266</v>
+        <v>433</v>
       </c>
       <c r="G2" t="n">
-        <v>540</v>
+        <v>790</v>
       </c>
       <c r="H2" t="n">
-        <v>354</v>
+        <v>551</v>
       </c>
       <c r="I2" t="n">
-        <v>4458</v>
+        <v>5973</v>
       </c>
       <c r="J2" t="n">
-        <v>1232</v>
+        <v>1613</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="E3" t="n">
+        <v>256</v>
+      </c>
+      <c r="F3" t="n">
+        <v>180</v>
+      </c>
+      <c r="G3" t="n">
+        <v>322</v>
+      </c>
+      <c r="H3" t="n">
+        <v>175</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1509</v>
+      </c>
+      <c r="J3" t="n">
+        <v>584</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>69</v>
+      </c>
+      <c r="C4" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E4" t="n">
+        <v>141</v>
+      </c>
+      <c r="F4" t="n">
+        <v>157</v>
+      </c>
+      <c r="G4" t="n">
+        <v>377</v>
+      </c>
+      <c r="H4" t="n">
+        <v>214</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1505</v>
+      </c>
+      <c r="J4" t="n">
+        <v>528</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -563,31 +563,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="C4" t="n">
-        <v>37.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>3.73</v>
+        <v>7.46</v>
       </c>
       <c r="E4" t="n">
-        <v>141</v>
+        <v>218</v>
       </c>
       <c r="F4" t="n">
-        <v>157</v>
+        <v>379</v>
       </c>
       <c r="G4" t="n">
-        <v>377</v>
+        <v>572</v>
       </c>
       <c r="H4" t="n">
-        <v>214</v>
+        <v>610</v>
       </c>
       <c r="I4" t="n">
-        <v>1505</v>
+        <v>3120</v>
       </c>
       <c r="J4" t="n">
-        <v>528</v>
+        <v>1081</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -563,13 +563,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" t="n">
-        <v>74.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>7.46</v>
+        <v>7.51</v>
       </c>
       <c r="E4" t="n">
         <v>218</v>
@@ -584,10 +584,10 @@
         <v>610</v>
       </c>
       <c r="I4" t="n">
-        <v>3120</v>
+        <v>4635</v>
       </c>
       <c r="J4" t="n">
-        <v>1081</v>
+        <v>1362</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -563,13 +563,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C4" t="n">
-        <v>75.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>7.51</v>
+        <v>7.56</v>
       </c>
       <c r="E4" t="n">
         <v>218</v>
@@ -584,10 +584,10 @@
         <v>610</v>
       </c>
       <c r="I4" t="n">
-        <v>4635</v>
+        <v>6150</v>
       </c>
       <c r="J4" t="n">
-        <v>1362</v>
+        <v>1643</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,7 +594,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>92</v>
+      </c>
+      <c r="F5" t="n">
+        <v>199</v>
+      </c>
+      <c r="G5" t="n">
+        <v>223</v>
+      </c>
+      <c r="H5" t="n">
+        <v>221</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1517</v>
+      </c>
+      <c r="J5" t="n">
+        <v>496</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
@@ -623,10 +623,10 @@
         <v>221</v>
       </c>
       <c r="I5" t="n">
-        <v>1517</v>
+        <v>3053</v>
       </c>
       <c r="J5" t="n">
-        <v>496</v>
+        <v>771</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
@@ -623,10 +623,10 @@
         <v>221</v>
       </c>
       <c r="I5" t="n">
-        <v>3053</v>
+        <v>4591</v>
       </c>
       <c r="J5" t="n">
-        <v>771</v>
+        <v>996</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
@@ -623,10 +623,10 @@
         <v>221</v>
       </c>
       <c r="I5" t="n">
-        <v>4591</v>
+        <v>6129</v>
       </c>
       <c r="J5" t="n">
-        <v>996</v>
+        <v>1221</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
@@ -623,10 +623,10 @@
         <v>221</v>
       </c>
       <c r="I5" t="n">
-        <v>6129</v>
+        <v>7670</v>
       </c>
       <c r="J5" t="n">
-        <v>1221</v>
+        <v>1396</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
@@ -623,10 +623,10 @@
         <v>221</v>
       </c>
       <c r="I5" t="n">
-        <v>7670</v>
+        <v>9211</v>
       </c>
       <c r="J5" t="n">
-        <v>1396</v>
+        <v>1571</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
@@ -623,7 +623,7 @@
         <v>221</v>
       </c>
       <c r="I5" t="n">
-        <v>9211</v>
+        <v>10813</v>
       </c>
       <c r="J5" t="n">
         <v>1571</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>69</v>
+      </c>
+      <c r="C6" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E6" t="n">
+        <v>121</v>
+      </c>
+      <c r="F6" t="n">
+        <v>176</v>
+      </c>
+      <c r="G6" t="n">
+        <v>371</v>
+      </c>
+      <c r="H6" t="n">
+        <v>239</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1602</v>
+      </c>
+      <c r="J6" t="n">
+        <v>492</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n">
-        <v>37.3</v>
+        <v>37.8</v>
       </c>
       <c r="D6" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="E6" t="n">
         <v>121</v>
@@ -662,7 +662,7 @@
         <v>239</v>
       </c>
       <c r="I6" t="n">
-        <v>1602</v>
+        <v>3256</v>
       </c>
       <c r="J6" t="n">
         <v>492</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C7" t="n">
+        <v>34</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>136</v>
+      </c>
+      <c r="F7" t="n">
+        <v>166</v>
+      </c>
+      <c r="G7" t="n">
+        <v>262</v>
+      </c>
+      <c r="H7" t="n">
+        <v>186</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1654</v>
+      </c>
+      <c r="J7" t="n">
+        <v>398</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="E7" t="n">
         <v>136</v>
@@ -701,7 +701,7 @@
         <v>186</v>
       </c>
       <c r="I7" t="n">
-        <v>1654</v>
+        <v>3335</v>
       </c>
       <c r="J7" t="n">
         <v>398</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,7 +711,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>69</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E8" t="n">
+        <v>109</v>
+      </c>
+      <c r="F8" t="n">
+        <v>192</v>
+      </c>
+      <c r="G8" t="n">
+        <v>348</v>
+      </c>
+      <c r="H8" t="n">
+        <v>256</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1681</v>
+      </c>
+      <c r="J8" t="n">
+        <v>457</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,7 +750,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>63</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>132</v>
+      </c>
+      <c r="F9" t="n">
+        <v>166</v>
+      </c>
+      <c r="G9" t="n">
+        <v>264</v>
+      </c>
+      <c r="H9" t="n">
+        <v>184</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1705</v>
+      </c>
+      <c r="J9" t="n">
+        <v>396</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,50 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>85</v>
+      </c>
+      <c r="C10" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="E10" t="n">
+        <v>236</v>
+      </c>
+      <c r="F10" t="n">
+        <v>220</v>
+      </c>
+      <c r="G10" t="n">
+        <v>362</v>
+      </c>
+      <c r="H10" t="n">
+        <v>241</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1748</v>
+      </c>
+      <c r="J10" t="n">
+        <v>598</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>熔断(部分数据)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>积分余额不足，当前调用积分0.5，剩余积分0.3；本次调用未执行。请前往 https://redfox.hk/dashboard/recharge 充值后重试。 (code=3201)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,6 +834,46 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>63</v>
+      </c>
+      <c r="C11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>135</v>
+      </c>
+      <c r="F11" t="n">
+        <v>161</v>
+      </c>
+      <c r="G11" t="n">
+        <v>246</v>
+      </c>
+      <c r="H11" t="n">
+        <v>192</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1834</v>
+      </c>
+      <c r="J11" t="n">
+        <v>381</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,7 +872,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>69</v>
+      </c>
+      <c r="C12" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E12" t="n">
+        <v>104</v>
+      </c>
+      <c r="F12" t="n">
+        <v>184</v>
+      </c>
+      <c r="G12" t="n">
+        <v>369</v>
+      </c>
+      <c r="H12" t="n">
+        <v>216</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1865</v>
+      </c>
+      <c r="J12" t="n">
+        <v>473</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>63</v>
+      </c>
+      <c r="C13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>117</v>
+      </c>
+      <c r="F13" t="n">
+        <v>169</v>
+      </c>
+      <c r="G13" t="n">
+        <v>242</v>
+      </c>
+      <c r="H13" t="n">
+        <v>180</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1893</v>
+      </c>
+      <c r="J13" t="n">
+        <v>359</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>69</v>
+      </c>
+      <c r="C14" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E14" t="n">
+        <v>103</v>
+      </c>
+      <c r="F14" t="n">
+        <v>181</v>
+      </c>
+      <c r="G14" t="n">
+        <v>360</v>
+      </c>
+      <c r="H14" t="n">
+        <v>205</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1914</v>
+      </c>
+      <c r="J14" t="n">
+        <v>463</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,7 +989,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>63</v>
+      </c>
+      <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>110</v>
+      </c>
+      <c r="F15" t="n">
+        <v>162</v>
+      </c>
+      <c r="G15" t="n">
+        <v>249</v>
+      </c>
+      <c r="H15" t="n">
+        <v>170</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J15" t="n">
+        <v>359</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,7 +1028,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>69</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E16" t="n">
+        <v>97</v>
+      </c>
+      <c r="F16" t="n">
+        <v>175</v>
+      </c>
+      <c r="G16" t="n">
+        <v>361</v>
+      </c>
+      <c r="H16" t="n">
+        <v>212</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1973</v>
+      </c>
+      <c r="J16" t="n">
+        <v>458</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,7 +1067,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>91</v>
+      </c>
+      <c r="C17" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="E17" t="n">
+        <v>210</v>
+      </c>
+      <c r="F17" t="n">
+        <v>218</v>
+      </c>
+      <c r="G17" t="n">
+        <v>306</v>
+      </c>
+      <c r="H17" t="n">
+        <v>187</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J17" t="n">
+        <v>516</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,7 +1106,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>69</v>
+      </c>
+      <c r="C18" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E18" t="n">
+        <v>129</v>
+      </c>
+      <c r="F18" t="n">
+        <v>157</v>
+      </c>
+      <c r="G18" t="n">
+        <v>346</v>
+      </c>
+      <c r="H18" t="n">
+        <v>217</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2130</v>
+      </c>
+      <c r="J18" t="n">
+        <v>475</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,7 +1145,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>63</v>
+      </c>
+      <c r="C19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>122</v>
+      </c>
+      <c r="F19" t="n">
+        <v>171</v>
+      </c>
+      <c r="G19" t="n">
+        <v>243</v>
+      </c>
+      <c r="H19" t="n">
+        <v>180</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2177</v>
+      </c>
+      <c r="J19" t="n">
+        <v>365</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,7 +1184,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>69</v>
+      </c>
+      <c r="C20" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E20" t="n">
+        <v>110</v>
+      </c>
+      <c r="F20" t="n">
+        <v>194</v>
+      </c>
+      <c r="G20" t="n">
+        <v>366</v>
+      </c>
+      <c r="H20" t="n">
+        <v>207</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2210</v>
+      </c>
+      <c r="J20" t="n">
+        <v>476</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1223,7 +1223,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>63</v>
+      </c>
+      <c r="C21" t="n">
+        <v>34</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>118</v>
+      </c>
+      <c r="F21" t="n">
+        <v>179</v>
+      </c>
+      <c r="G21" t="n">
+        <v>252</v>
+      </c>
+      <c r="H21" t="n">
+        <v>184</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2248</v>
+      </c>
+      <c r="J21" t="n">
+        <v>370</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,7 +1262,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>69</v>
+      </c>
+      <c r="C22" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E22" t="n">
+        <v>118</v>
+      </c>
+      <c r="F22" t="n">
+        <v>191</v>
+      </c>
+      <c r="G22" t="n">
+        <v>371</v>
+      </c>
+      <c r="H22" t="n">
+        <v>224</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2280</v>
+      </c>
+      <c r="J22" t="n">
+        <v>489</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,7 +1301,222 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>跳过(今日无更新)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>红狐接口不可用，跳过爬取</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>跳过(今日无更新)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>红狐接口不可用，跳过爬取</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>跳过(今日无更新)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>红狐接口不可用，跳过爬取</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>跳过(今日无更新)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>红狐接口不可用，跳过爬取</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>64</v>
+      </c>
+      <c r="C27" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E27" t="n">
+        <v>175</v>
+      </c>
+      <c r="F27" t="n">
+        <v>133</v>
+      </c>
+      <c r="G27" t="n">
+        <v>290</v>
+      </c>
+      <c r="H27" t="n">
+        <v>157</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2318</v>
+      </c>
+      <c r="J27" t="n">
+        <v>465</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,7 +1516,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>69</v>
+      </c>
+      <c r="C28" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E28" t="n">
+        <v>121</v>
+      </c>
+      <c r="F28" t="n">
+        <v>197</v>
+      </c>
+      <c r="G28" t="n">
+        <v>363</v>
+      </c>
+      <c r="H28" t="n">
+        <v>242</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2415</v>
+      </c>
+      <c r="J28" t="n">
+        <v>509</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1555,7 +1555,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>63</v>
+      </c>
+      <c r="C29" t="n">
+        <v>34</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>116</v>
+      </c>
+      <c r="F29" t="n">
+        <v>187</v>
+      </c>
+      <c r="G29" t="n">
+        <v>257</v>
+      </c>
+      <c r="H29" t="n">
+        <v>190</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2453</v>
+      </c>
+      <c r="J29" t="n">
+        <v>373</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1594,7 +1594,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>69</v>
+      </c>
+      <c r="C30" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E30" t="n">
+        <v>117</v>
+      </c>
+      <c r="F30" t="n">
+        <v>196</v>
+      </c>
+      <c r="G30" t="n">
+        <v>373</v>
+      </c>
+      <c r="H30" t="n">
+        <v>235</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2469</v>
+      </c>
+      <c r="J30" t="n">
+        <v>490</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,7 +1633,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>92</v>
+      </c>
+      <c r="C31" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E31" t="n">
+        <v>212</v>
+      </c>
+      <c r="F31" t="n">
+        <v>250</v>
+      </c>
+      <c r="G31" t="n">
+        <v>312</v>
+      </c>
+      <c r="H31" t="n">
+        <v>224</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2501</v>
+      </c>
+      <c r="J31" t="n">
+        <v>524</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,7 +1672,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>69</v>
+      </c>
+      <c r="C32" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E32" t="n">
+        <v>134</v>
+      </c>
+      <c r="F32" t="n">
+        <v>192</v>
+      </c>
+      <c r="G32" t="n">
+        <v>370</v>
+      </c>
+      <c r="H32" t="n">
+        <v>234</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2615</v>
+      </c>
+      <c r="J32" t="n">
+        <v>504</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1711,7 +1711,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>63</v>
+      </c>
+      <c r="C33" t="n">
+        <v>34</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>121</v>
+      </c>
+      <c r="F33" t="n">
+        <v>180</v>
+      </c>
+      <c r="G33" t="n">
+        <v>257</v>
+      </c>
+      <c r="H33" t="n">
+        <v>184</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2651</v>
+      </c>
+      <c r="J33" t="n">
+        <v>378</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1750,7 +1750,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>69</v>
+      </c>
+      <c r="C34" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E34" t="n">
+        <v>115</v>
+      </c>
+      <c r="F34" t="n">
+        <v>201</v>
+      </c>
+      <c r="G34" t="n">
+        <v>348</v>
+      </c>
+      <c r="H34" t="n">
+        <v>252</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2671</v>
+      </c>
+      <c r="J34" t="n">
+        <v>488</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1789,7 +1789,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>63</v>
+      </c>
+      <c r="C35" t="n">
+        <v>34</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>111</v>
+      </c>
+      <c r="F35" t="n">
+        <v>169</v>
+      </c>
+      <c r="G35" t="n">
+        <v>243</v>
+      </c>
+      <c r="H35" t="n">
+        <v>194</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2701</v>
+      </c>
+      <c r="J35" t="n">
+        <v>354</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,7 +1828,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>69</v>
+      </c>
+      <c r="C36" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E36" t="n">
+        <v>104</v>
+      </c>
+      <c r="F36" t="n">
+        <v>200</v>
+      </c>
+      <c r="G36" t="n">
+        <v>331</v>
+      </c>
+      <c r="H36" t="n">
+        <v>254</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2734</v>
+      </c>
+      <c r="J36" t="n">
+        <v>435</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1867,7 +1867,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>63</v>
+      </c>
+      <c r="C37" t="n">
+        <v>34</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>105</v>
+      </c>
+      <c r="F37" t="n">
+        <v>161</v>
+      </c>
+      <c r="G37" t="n">
+        <v>227</v>
+      </c>
+      <c r="H37" t="n">
+        <v>205</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2753</v>
+      </c>
+      <c r="J37" t="n">
+        <v>332</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1906,7 +1906,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>97</v>
+      </c>
+      <c r="C38" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E38" t="n">
+        <v>162</v>
+      </c>
+      <c r="F38" t="n">
+        <v>285</v>
+      </c>
+      <c r="G38" t="n">
+        <v>386</v>
+      </c>
+      <c r="H38" t="n">
+        <v>298</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2776</v>
+      </c>
+      <c r="J38" t="n">
+        <v>548</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1945,7 +1945,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>63</v>
+      </c>
+      <c r="C39" t="n">
+        <v>34</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>117</v>
+      </c>
+      <c r="F39" t="n">
+        <v>151</v>
+      </c>
+      <c r="G39" t="n">
+        <v>224</v>
+      </c>
+      <c r="H39" t="n">
+        <v>200</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2854</v>
+      </c>
+      <c r="J39" t="n">
+        <v>341</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,7 +1984,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>69</v>
+      </c>
+      <c r="C40" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E40" t="n">
+        <v>96</v>
+      </c>
+      <c r="F40" t="n">
+        <v>199</v>
+      </c>
+      <c r="G40" t="n">
+        <v>355</v>
+      </c>
+      <c r="H40" t="n">
+        <v>244</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2879</v>
+      </c>
+      <c r="J40" t="n">
+        <v>451</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,7 +2023,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>63</v>
+      </c>
+      <c r="C41" t="n">
+        <v>34</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>109</v>
+      </c>
+      <c r="F41" t="n">
+        <v>151</v>
+      </c>
+      <c r="G41" t="n">
+        <v>226</v>
+      </c>
+      <c r="H41" t="n">
+        <v>203</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2910</v>
+      </c>
+      <c r="J41" t="n">
+        <v>335</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2062,7 +2062,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>69</v>
+      </c>
+      <c r="C42" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E42" t="n">
+        <v>106</v>
+      </c>
+      <c r="F42" t="n">
+        <v>191</v>
+      </c>
+      <c r="G42" t="n">
+        <v>333</v>
+      </c>
+      <c r="H42" t="n">
+        <v>262</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2940</v>
+      </c>
+      <c r="J42" t="n">
+        <v>439</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,7 +2101,50 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>11</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E43" t="n">
+        <v>82</v>
+      </c>
+      <c r="F43" t="n">
+        <v>99</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2966</v>
+      </c>
+      <c r="J43" t="n">
+        <v>82</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>熔断(部分数据)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>积分不足，请完成支付后重试 (code=3210)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2146,6 +2146,46 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>92</v>
+      </c>
+      <c r="C44" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E44" t="n">
+        <v>174</v>
+      </c>
+      <c r="F44" t="n">
+        <v>217</v>
+      </c>
+      <c r="G44" t="n">
+        <v>257</v>
+      </c>
+      <c r="H44" t="n">
+        <v>231</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2968</v>
+      </c>
+      <c r="J44" t="n">
+        <v>431</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C44" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="D44" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="E44" t="n">
         <v>174</v>
@@ -2174,7 +2174,7 @@
         <v>231</v>
       </c>
       <c r="I44" t="n">
-        <v>2968</v>
+        <v>6014</v>
       </c>
       <c r="J44" t="n">
         <v>431</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C44" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="D44" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
       <c r="E44" t="n">
         <v>174</v>
@@ -2174,7 +2174,7 @@
         <v>231</v>
       </c>
       <c r="I44" t="n">
-        <v>6014</v>
+        <v>9060</v>
       </c>
       <c r="J44" t="n">
         <v>431</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
       <c r="D44" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="E44" t="n">
         <v>174</v>
@@ -2174,7 +2174,7 @@
         <v>231</v>
       </c>
       <c r="I44" t="n">
-        <v>9060</v>
+        <v>12106</v>
       </c>
       <c r="J44" t="n">
         <v>431</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2184,7 +2184,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>69</v>
+      </c>
+      <c r="C45" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E45" t="n">
+        <v>139</v>
+      </c>
+      <c r="F45" t="n">
+        <v>154</v>
+      </c>
+      <c r="G45" t="n">
+        <v>323</v>
+      </c>
+      <c r="H45" t="n">
+        <v>254</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3046</v>
+      </c>
+      <c r="J45" t="n">
+        <v>462</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,7 +2223,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>63</v>
+      </c>
+      <c r="C46" t="n">
+        <v>34</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>119</v>
+      </c>
+      <c r="F46" t="n">
+        <v>129</v>
+      </c>
+      <c r="G46" t="n">
+        <v>214</v>
+      </c>
+      <c r="H46" t="n">
+        <v>193</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3083</v>
+      </c>
+      <c r="J46" t="n">
+        <v>333</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C46" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="D46" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="E46" t="n">
         <v>119</v>
@@ -2252,7 +2252,7 @@
         <v>193</v>
       </c>
       <c r="I46" t="n">
-        <v>3083</v>
+        <v>6144</v>
       </c>
       <c r="J46" t="n">
         <v>333</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2262,7 +2262,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>69</v>
+      </c>
+      <c r="C47" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E47" t="n">
+        <v>125</v>
+      </c>
+      <c r="F47" t="n">
+        <v>158</v>
+      </c>
+      <c r="G47" t="n">
+        <v>324</v>
+      </c>
+      <c r="H47" t="n">
+        <v>247</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3061</v>
+      </c>
+      <c r="J47" t="n">
+        <v>449</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2301,7 +2301,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>63</v>
+      </c>
+      <c r="C48" t="n">
+        <v>34</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>119</v>
+      </c>
+      <c r="F48" t="n">
+        <v>127</v>
+      </c>
+      <c r="G48" t="n">
+        <v>223</v>
+      </c>
+      <c r="H48" t="n">
+        <v>186</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3079</v>
+      </c>
+      <c r="J48" t="n">
+        <v>342</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2340,7 +2340,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>69</v>
+      </c>
+      <c r="C49" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E49" t="n">
+        <v>125</v>
+      </c>
+      <c r="F49" t="n">
+        <v>140</v>
+      </c>
+      <c r="G49" t="n">
+        <v>334</v>
+      </c>
+      <c r="H49" t="n">
+        <v>238</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3095</v>
+      </c>
+      <c r="J49" t="n">
+        <v>459</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
